--- a/data/trans_orig/P79A_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P79A_R-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9118</t>
+          <t>12514</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>3473</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24175</t>
+          <t>32849</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21111</t>
+          <t>21163</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10812</t>
+          <t>10766</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40066</t>
+          <t>36286</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>30229</t>
+          <t>33677</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15259</t>
+          <t>19190</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52396</t>
+          <t>58060</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>390869</t>
+          <t>395279</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>375812</t>
+          <t>374944</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>398065</t>
+          <t>404320</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>292089</t>
+          <t>341349</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>273134</t>
+          <t>326226</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>302388</t>
+          <t>351746</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>682958</t>
+          <t>736628</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>660791</t>
+          <t>712245</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>697928</t>
+          <t>751115</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14350</t>
+          <t>14087</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>6860</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29231</t>
+          <t>29629</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>10571</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>4794</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16992</t>
+          <t>19908</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>22287</t>
+          <t>24658</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12367</t>
+          <t>13668</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38818</t>
+          <t>41506</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>409197</t>
+          <t>462803</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>394316</t>
+          <t>447261</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>417987</t>
+          <t>470030</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>504156</t>
+          <t>491162</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>495101</t>
+          <t>481825</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>509202</t>
+          <t>496939</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>913353</t>
+          <t>953965</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>896822</t>
+          <t>937117</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>923273</t>
+          <t>964955</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15105</t>
+          <t>18558</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8823</t>
+          <t>11591</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24803</t>
+          <t>28384</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16004</t>
+          <t>18968</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9926</t>
+          <t>12752</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24537</t>
+          <t>27768</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>31110</t>
+          <t>37526</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21713</t>
+          <t>27237</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43583</t>
+          <t>50583</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>521233</t>
+          <t>602279</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>511535</t>
+          <t>592453</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>527515</t>
+          <t>609246</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>575998</t>
+          <t>604225</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>567465</t>
+          <t>595425</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>582076</t>
+          <t>610441</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1097230</t>
+          <t>1206503</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1084757</t>
+          <t>1193446</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1106627</t>
+          <t>1216792</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14311</t>
+          <t>18086</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4306</t>
+          <t>9880</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26356</t>
+          <t>28463</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11259</t>
+          <t>12740</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6508</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17196</t>
+          <t>18943</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>25570</t>
+          <t>30827</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14599</t>
+          <t>21619</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38311</t>
+          <t>41632</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>873475</t>
+          <t>682531</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>861430</t>
+          <t>672154</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>883480</t>
+          <t>690737</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>701622</t>
+          <t>724146</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>695685</t>
+          <t>717943</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>706373</t>
+          <t>729119</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1575097</t>
+          <t>1406677</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1562356</t>
+          <t>1395872</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1586068</t>
+          <t>1415885</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>12849</t>
+          <t>16217</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7691</t>
+          <t>9544</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21672</t>
+          <t>27107</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>12591</t>
+          <t>14372</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>9436</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18880</t>
+          <t>21915</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>25439</t>
+          <t>30589</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17359</t>
+          <t>21288</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35123</t>
+          <t>42170</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>548385</t>
+          <t>593129</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>539562</t>
+          <t>582239</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>553543</t>
+          <t>599802</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>535314</t>
+          <t>594483</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>529025</t>
+          <t>586940</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>540052</t>
+          <t>599419</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1083700</t>
+          <t>1187613</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1074016</t>
+          <t>1176032</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1091780</t>
+          <t>1196914</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8667</t>
+          <t>9804</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3716</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>1689</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7534</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>8573</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3499</t>
+          <t>4453</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13666</t>
+          <t>14132</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>363686</t>
+          <t>402223</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>359498</t>
+          <t>397276</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>366286</t>
+          <t>405052</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>604929</t>
+          <t>435450</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>600834</t>
+          <t>431337</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>607810</t>
+          <t>437477</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>968615</t>
+          <t>837673</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>962867</t>
+          <t>832114</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>973034</t>
+          <t>841793</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4724</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>3791</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -2896,27 +2896,27 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>281818</t>
+          <t>309156</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>278035</t>
+          <t>304314</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>423972</t>
+          <t>461860</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>420892</t>
+          <t>458126</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>425184</t>
+          <t>463575</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>705789</t>
+          <t>771016</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>701795</t>
+          <t>766695</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>707495</t>
+          <t>773572</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>71153</t>
+          <t>85362</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>51781</t>
+          <t>66461</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>95956</t>
+          <t>111769</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>74199</t>
+          <t>84279</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>54238</t>
+          <t>67586</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>95737</t>
+          <t>106853</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>145352</t>
+          <t>169641</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>115676</t>
+          <t>141286</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>180662</t>
+          <t>202044</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3388664</t>
+          <t>3447400</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3363861</t>
+          <t>3420993</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3408036</t>
+          <t>3466301</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3638081</t>
+          <t>3652675</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3616543</t>
+          <t>3630101</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3658042</t>
+          <t>3669368</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>7026745</t>
+          <t>7100075</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6991435</t>
+          <t>7067672</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7056421</t>
+          <t>7128430</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
